--- a/data/FANUC_Motor_Specs_Direct.xlsx
+++ b/data/FANUC_Motor_Specs_Direct.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e11338\Desktop\Feed System GAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9B7B60-C9C3-4B6F-82B8-6D455439C574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC69AD77-9DED-414B-832B-054FAB699323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17015" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17016" uniqueCount="333">
   <si>
     <t>Model</t>
   </si>
@@ -1021,6 +1021,10 @@
   <si>
     <t>0.26</t>
   </si>
+  <si>
+    <t>page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -9229,7 +9233,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D62FE6-63FC-49E0-AAAB-D2C3786CE405}">
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
@@ -9244,7 +9248,7 @@
     <col min="15" max="15" width="33.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9290,8 +9294,11 @@
       <c r="O1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -9337,8 +9344,11 @@
       <c r="O2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -9384,8 +9394,11 @@
       <c r="O3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -9431,8 +9444,11 @@
       <c r="O4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -9478,8 +9494,11 @@
       <c r="O5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -9525,8 +9544,11 @@
       <c r="O6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -9572,8 +9594,11 @@
       <c r="O7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -9619,8 +9644,11 @@
       <c r="O8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -9666,8 +9694,11 @@
       <c r="O9">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -9713,8 +9744,11 @@
       <c r="O10">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -9760,8 +9794,11 @@
       <c r="O11">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -9807,8 +9844,11 @@
       <c r="O12">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -9854,8 +9894,11 @@
       <c r="O13">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -9901,8 +9944,11 @@
       <c r="O14">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -9948,8 +9994,11 @@
       <c r="O15">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -9995,8 +10044,11 @@
       <c r="O16">
         <v>80</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -10042,8 +10094,11 @@
       <c r="O17">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -10089,8 +10144,11 @@
       <c r="O18">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -10136,8 +10194,11 @@
       <c r="O19">
         <v>80</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -10183,8 +10244,11 @@
       <c r="O20">
         <v>160</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>78</v>
       </c>
@@ -10230,8 +10294,11 @@
       <c r="O21">
         <v>160</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>79</v>
       </c>
@@ -10277,8 +10344,11 @@
       <c r="O22">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P22">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -10324,8 +10394,11 @@
       <c r="O23">
         <v>40</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P23">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>81</v>
       </c>
@@ -10371,8 +10444,11 @@
       <c r="O24">
         <v>80</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -10418,8 +10494,11 @@
       <c r="O25">
         <v>160</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -10465,8 +10544,11 @@
       <c r="O26">
         <v>160</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P26">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -10512,8 +10594,11 @@
       <c r="O27">
         <v>80</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>85</v>
       </c>
@@ -10559,8 +10644,11 @@
       <c r="O28">
         <v>160</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P28">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -10606,8 +10694,11 @@
       <c r="O29">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P29">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -10653,8 +10744,11 @@
       <c r="O30">
         <v>160</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P30">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -10700,8 +10794,11 @@
       <c r="O31">
         <v>160</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -10747,8 +10844,11 @@
       <c r="O32">
         <v>360</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -10794,8 +10894,11 @@
       <c r="O33">
         <v>160</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P33">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -10841,8 +10944,11 @@
       <c r="O34">
         <v>360</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P34">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>92</v>
       </c>
@@ -10888,8 +10994,11 @@
       <c r="O35">
         <v>360</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -10935,8 +11044,11 @@
       <c r="O36">
         <v>360</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P36">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -10982,8 +11094,11 @@
       <c r="O37">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P37">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -11029,8 +11144,11 @@
       <c r="O38">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P38">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -11076,8 +11194,11 @@
       <c r="O39">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P39">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>97</v>
       </c>
@@ -11123,8 +11244,11 @@
       <c r="O40">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P40">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>98</v>
       </c>
@@ -11170,8 +11294,11 @@
       <c r="O41">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P41">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>99</v>
       </c>
@@ -11217,8 +11344,11 @@
       <c r="O42">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P42">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -11264,8 +11394,11 @@
       <c r="O43">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P43">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>101</v>
       </c>
@@ -11311,8 +11444,11 @@
       <c r="O44">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P44">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>102</v>
       </c>
@@ -11358,8 +11494,11 @@
       <c r="O45">
         <v>20</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P45">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -11405,8 +11544,11 @@
       <c r="O46">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P46">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -11452,8 +11594,11 @@
       <c r="O47">
         <v>40</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P47">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -11499,8 +11644,11 @@
       <c r="O48">
         <v>40</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P48">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -11546,8 +11694,11 @@
       <c r="O49">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>107</v>
       </c>
@@ -11593,8 +11744,11 @@
       <c r="O50">
         <v>20</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P50">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -11640,8 +11794,11 @@
       <c r="O51">
         <v>40</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P51">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>109</v>
       </c>
@@ -11687,8 +11844,11 @@
       <c r="O52">
         <v>80</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P52">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>110</v>
       </c>
@@ -11734,8 +11894,11 @@
       <c r="O53">
         <v>80</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P53">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>111</v>
       </c>
@@ -11781,8 +11944,11 @@
       <c r="O54">
         <v>40</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P54">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>112</v>
       </c>
@@ -11828,8 +11994,11 @@
       <c r="O55">
         <v>20</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P55">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>113</v>
       </c>
@@ -11875,8 +12044,11 @@
       <c r="O56">
         <v>40</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P56">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>114</v>
       </c>
@@ -11922,8 +12094,11 @@
       <c r="O57">
         <v>80</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P57">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -11969,8 +12144,11 @@
       <c r="O58">
         <v>80</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P58">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -12016,8 +12194,11 @@
       <c r="O59">
         <v>40</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P59">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>117</v>
       </c>
@@ -12063,8 +12244,11 @@
       <c r="O60">
         <v>80</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P60">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -12110,8 +12294,11 @@
       <c r="O61">
         <v>40</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P61">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>119</v>
       </c>
@@ -12157,8 +12344,11 @@
       <c r="O62">
         <v>80</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P62">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -12204,8 +12394,11 @@
       <c r="O63">
         <v>80</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P63">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -12251,8 +12444,11 @@
       <c r="O64">
         <v>180</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P64">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>122</v>
       </c>
@@ -12298,8 +12494,11 @@
       <c r="O65">
         <v>80</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P65">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>123</v>
       </c>
@@ -12345,8 +12544,11 @@
       <c r="O66">
         <v>180</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P66">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>124</v>
       </c>
@@ -12392,8 +12594,11 @@
       <c r="O67">
         <v>180</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P67">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>124</v>
       </c>
@@ -12439,8 +12644,11 @@
       <c r="O68">
         <v>180</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P68">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>126</v>
       </c>
@@ -12486,8 +12694,11 @@
       <c r="O69">
         <v>180</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P69">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>126</v>
       </c>
@@ -12533,8 +12744,11 @@
       <c r="O70">
         <v>180</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P70">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>127</v>
       </c>
@@ -12580,8 +12794,11 @@
       <c r="O71">
         <v>20</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P71">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>129</v>
       </c>
@@ -12627,8 +12844,11 @@
       <c r="O72">
         <v>20</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P72">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>130</v>
       </c>
@@ -12674,8 +12894,11 @@
       <c r="O73">
         <v>20</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P73">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>131</v>
       </c>
@@ -12721,8 +12944,11 @@
       <c r="O74">
         <v>40</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P74">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>132</v>
       </c>
@@ -12768,8 +12994,11 @@
       <c r="O75">
         <v>40</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P75">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>133</v>
       </c>
@@ -12815,8 +13044,11 @@
       <c r="O76">
         <v>80</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P76">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>134</v>
       </c>
@@ -12862,8 +13094,11 @@
       <c r="O77">
         <v>40</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P77">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>135</v>
       </c>
@@ -12909,8 +13144,11 @@
       <c r="O78">
         <v>80</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P78">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>136</v>
       </c>
@@ -12956,8 +13194,11 @@
       <c r="O79">
         <v>80</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P79">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>137</v>
       </c>
@@ -13003,8 +13244,11 @@
       <c r="O80">
         <v>160</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P80">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>138</v>
       </c>
@@ -13050,8 +13294,11 @@
       <c r="O81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P81">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>139</v>
       </c>
@@ -13097,8 +13344,11 @@
       <c r="O82">
         <v>160</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P82">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>140</v>
       </c>
@@ -13144,8 +13394,11 @@
       <c r="O83">
         <v>160</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P83">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>141</v>
       </c>
@@ -13191,8 +13444,11 @@
       <c r="O84">
         <v>160</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P84">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>141</v>
       </c>
@@ -13238,8 +13494,11 @@
       <c r="O85">
         <v>160</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P85">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>142</v>
       </c>
@@ -13285,8 +13544,11 @@
       <c r="O86">
         <v>10</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P86">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>143</v>
       </c>
@@ -13332,8 +13594,11 @@
       <c r="O87">
         <v>20</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P87">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>144</v>
       </c>
@@ -13379,8 +13644,11 @@
       <c r="O88">
         <v>20</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P88">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>145</v>
       </c>
@@ -13426,8 +13694,11 @@
       <c r="O89">
         <v>40</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P89">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>146</v>
       </c>
@@ -13473,8 +13744,11 @@
       <c r="O90">
         <v>20</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P90">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>147</v>
       </c>
@@ -13520,8 +13794,11 @@
       <c r="O91">
         <v>40</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P91">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>148</v>
       </c>
@@ -13567,8 +13844,11 @@
       <c r="O92">
         <v>40</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P92">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>149</v>
       </c>
@@ -13614,8 +13894,11 @@
       <c r="O93">
         <v>80</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P93">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>150</v>
       </c>
@@ -13661,8 +13944,11 @@
       <c r="O94">
         <v>40</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P94">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>151</v>
       </c>
@@ -13708,8 +13994,11 @@
       <c r="O95">
         <v>80</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P95">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>152</v>
       </c>
@@ -13755,8 +14044,11 @@
       <c r="O96">
         <v>80</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P96">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>153</v>
       </c>
@@ -13802,8 +14094,11 @@
       <c r="O97">
         <v>80</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P97">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>153</v>
       </c>
@@ -13848,11 +14143,15 @@
       </c>
       <c r="O98">
         <v>80</v>
+      </c>
+      <c r="P98">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -103948,6 +104247,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="44.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
